--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EFE316A-468F-4C41-A1D2-B1CDD47A7ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EA08558-B216-4FA6-9BDF-3A48433F8D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -759,13 +759,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH05,S01aH04,S02aH03,S01aH02,S04aH04,S03aH04,S01aH03,S04aH02,S03aH02,S01aH05,S04aH03,S04aH05,S02aH02,S02aH04,S02aH05,S03aH03</t>
+    <t>S02aH02,S01aH04,S04aH02,S04aH05,S01aH02,S04aH04,S04aH03,S01aH05,S02aH04,S02aH05,S03aH05,S03aH02,S02aH03,S03aH03,S03aH04,S01aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S02aH01,S03aH01,S02aH06</t>
+    <t>S03aH01,S03aH06,S02aH01,S02aH06,S01aH06,S01aH01,S04aH01,S04aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S02aH01,S03aH01,S02aH06</v>
+        <v>S03aH01,S03aH06,S02aH01,S02aH06,S01aH06,S01aH01,S04aH01,S04aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH05,S01aH04,S02aH03,S01aH02,S04aH04,S03aH04,S01aH03,S04aH02,S03aH02,S01aH05,S04aH03,S04aH05,S02aH02,S02aH04,S02aH05,S03aH03</v>
+        <v>S02aH02,S01aH04,S04aH02,S04aH05,S01aH02,S04aH04,S04aH03,S01aH05,S02aH04,S02aH05,S03aH05,S03aH02,S02aH03,S03aH03,S03aH04,S01aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1488,7 +1488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE595FE-C501-48DE-888F-CE75664642E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A326C99-7A89-4373-A010-06E38AECAF34}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1594,7 +1594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73BBC7E-408E-47F1-AF40-A7DD62B9E585}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8F10A8-B3A4-47A4-A694-A7755BBDABDD}">
   <dimension ref="B9:O874"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24408,7 +24408,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D34B67B-C1A2-45A8-B430-AC17AD1360A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C6CF35-C68C-4276-9E0B-35D7658A5477}">
   <dimension ref="B9:DH83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37422,7 +37422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E927C0-96E2-443A-8972-BE22B1CDE280}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A987D918-733A-480E-AFF2-EC0D0079A60A}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37788,7 +37788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78310FD4-4198-4021-9D85-F3AE72054790}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69298BD-A1EB-4716-A424-8994B798BD7C}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38343,7 +38343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{524B48C5-305B-4BDD-AD74-C153E5A6651E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E59DB8-CE75-4284-827E-9E6AD95700C6}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38634,7 +38634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4A2CFF9-9A8E-42F7-9CE1-A37CBE843AD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60DFA18-54F3-4CE1-81B8-23A334A3AD16}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38974,7 +38974,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.2693666666666667</v>
+        <v>0.26936666666666664</v>
       </c>
       <c r="E33" t="s">
         <v>247</v>
@@ -39016,7 +39016,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.27806666666666663</v>
+        <v>0.27806666666666668</v>
       </c>
       <c r="E36" t="s">
         <v>247</v>
@@ -39030,7 +39030,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.29803333333333337</v>
+        <v>0.29803333333333332</v>
       </c>
       <c r="E37" t="s">
         <v>247</v>
@@ -39086,7 +39086,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.31070000000000003</v>
+        <v>0.31069999999999998</v>
       </c>
       <c r="E41" t="s">
         <v>247</v>
@@ -39142,7 +39142,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.25566666666666671</v>
+        <v>0.25566666666666665</v>
       </c>
       <c r="E45" t="s">
         <v>247</v>
@@ -39184,7 +39184,7 @@
         <v>41</v>
       </c>
       <c r="D48">
-        <v>0.33253333333333329</v>
+        <v>0.33253333333333335</v>
       </c>
       <c r="E48" t="s">
         <v>247</v>
@@ -39422,7 +39422,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.24773333333333336</v>
+        <v>0.24773333333333333</v>
       </c>
       <c r="E65" t="s">
         <v>247</v>
@@ -39702,7 +39702,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.27389999999999998</v>
+        <v>0.27390000000000003</v>
       </c>
       <c r="E85" t="s">
         <v>247</v>
@@ -39800,7 +39800,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.28523333333333328</v>
+        <v>0.28523333333333339</v>
       </c>
       <c r="E92" t="s">
         <v>247</v>
@@ -39912,7 +39912,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.4003666666666667</v>
+        <v>0.40036666666666659</v>
       </c>
       <c r="E100" t="s">
         <v>247</v>
@@ -39968,7 +39968,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.39750000000000002</v>
+        <v>0.39749999999999996</v>
       </c>
       <c r="E104" t="s">
         <v>247</v>
@@ -39982,7 +39982,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.30883333333333335</v>
+        <v>0.30883333333333329</v>
       </c>
       <c r="E105" t="s">
         <v>247</v>
@@ -40248,7 +40248,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.36246666666666671</v>
+        <v>0.36246666666666666</v>
       </c>
       <c r="E124" t="s">
         <v>247</v>
